--- a/StructureDefinition-openimis-enrolment-officer-practitioner-role.xlsx
+++ b/StructureDefinition-openimis-enrolment-officer-practitioner-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -10478,7 +10478,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>22</v>
@@ -10950,7 +10950,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>22</v>
@@ -11301,7 +11301,7 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>22</v>
@@ -11535,7 +11535,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>22</v>
@@ -11767,7 +11767,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>22</v>
@@ -15967,7 +15967,7 @@
         <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-enrolment-officer-practitioner-role.xlsx
+++ b/StructureDefinition-openimis-enrolment-officer-practitioner-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-enrolment-officer-practitioner-role.xlsx
+++ b/StructureDefinition-openimis-enrolment-officer-practitioner-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
